--- a/testdata/Data_Driven_Testing_Write_Excel.xlsx
+++ b/testdata/Data_Driven_Testing_Write_Excel.xlsx
@@ -6,45 +6,48 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="SheetA" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
-    <t>Java</t>
+    <t>fghj5678%^&amp;</t>
   </si>
   <si>
-    <t>12-05-2023</t>
+    <t>11/5/2026</t>
   </si>
   <si>
-    <t>Automation</t>
+    <t>SDFGDFGHJ#$%^&amp;</t>
   </si>
   <si>
-    <t>Selenium</t>
+    <t>0@#$%^&amp;+_</t>
   </si>
   <si>
-    <t>15-05-2023</t>
+    <t>a%tFF678%^&amp;</t>
   </si>
   <si>
-    <t>Appium</t>
+    <t>20/1/2024</t>
   </si>
   <si>
-    <t>18-05-2024</t>
+    <t>SDFGFGHJ#$%^&amp;</t>
   </si>
   <si>
-    <t>Restassured</t>
+    <t>$%^+-</t>
   </si>
   <si>
-    <t>30-05-2025</t>
+    <t>ioiu567909</t>
   </si>
   <si>
-    <t>C#</t>
+    <t>08/8/2026</t>
   </si>
   <si>
-    <t>31-05-2026</t>
+    <t>hjuiDFGHJ#$%^</t>
+  </si>
+  <si>
+    <t>@8$%i&amp;+p</t>
   </si>
 </sst>
 </file>
@@ -89,7 +92,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -102,49 +105,36 @@
       <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
+      <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="C5" t="s" s="0">
-        <v>2</v>
+      <c r="D3" t="s" s="0">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
